--- a/correction-tableaux-fsh/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/correction-tableaux-fsh/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:28:29+00:00</t>
+    <t>2026-06-18T08:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correction-tableaux-fsh/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/correction-tableaux-fsh/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:52:19+00:00</t>
+    <t>2026-06-18T09:16:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correction-tableaux-fsh/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/correction-tableaux-fsh/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:16:42+00:00</t>
+    <t>2026-06-18T09:28:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correction-tableaux-fsh/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/correction-tableaux-fsh/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:28:53+00:00</t>
+    <t>2026-06-18T09:52:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
